--- a/excel/endlessNightmare/EN07.xlsx
+++ b/excel/endlessNightmare/EN07.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\p2n\scripts\endlessNightmare\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\p2n\excel\endlessNightmare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798D5387-7787-40F5-BB56-9103F652B860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3017F827-6FF2-4CD8-93A3-DE32E352AE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{96D51E2F-743F-40BC-ACE2-2F53CD69DDD6}"/>
   </bookViews>
   <sheets>
     <sheet name="01" sheetId="4" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="1643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2429" uniqueCount="1637">
   <si>
     <t>speaker</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3480,30 +3480,6 @@
     <t>도대체 어떻게 여기까지 이르게 된 걸까?</t>
   </si>
   <si>
-    <t>이 폐허의 미궁에 갇혀 출구를 찾지 못한 채, 되돌아갈 수도 없게 된 걸까?</t>
-  </si>
-  <si>
-    <t>원진의 유혹을 듣고 심연에 속아 넘어간 걸까?</t>
-  </si>
-  <si>
-    <t>아니면 그녀가 추구한 사도가 그녀로 하여금 너무 많은 것을 묻게 하고, 너무 많은 것을 바라게 한 끝에,</t>
-  </si>
-  <si>
-    <t>한꺼번에 그 대가를 치르게 된 걸까?</t>
-  </si>
-  <si>
-    <t>지금 이 차가운 죽음의 물결 속에 있는 그녀는 또 어떤 심정일까?</t>
-  </si>
-  <si>
-    <t>여전히 당신이 익히 아는 그 호탕하고 자유로운 모습일까?</t>
-  </si>
-  <si>
-    <t>아니면 그녀가 배웅한 수많은 망령처럼, 혼란스럽고 고통스러워, 오래도록 배회하고 있을까?</t>
-  </si>
-  <si>
-    <t>그녀는 자신이 추구해 온 생사의 초월이, 백 년 후에도 여전히 헛된 말에 불과하다는 것과, 그녀가 구한 도 또한 끝없는 밤 아래 잠깐 스쳐 지나가는 미미한 빛 하나에 지나지 않는다는 사실을 알고 있을까?</t>
-  </si>
-  <si>
     <t>그녀는 이런 결말까지도 점쳐 보았던 걸까?</t>
   </si>
   <si>
@@ -5476,6 +5452,14 @@
   </si>
   <si>
     <t>당신의 만류는 관 속에서 공허하게 흩어졌다. 가슴의 부적이 타오르는 가운데, 당신은 '리진'의 몸을 계속 떠받친 채 조금씩 바깥으로 옮겨 갔다. 그리고 품에 안긴 사람이 점차 관 밖으로 모습을 드러내자, 얼어붙었던 공기가 다시 흐르기 시작했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 폐허의 미궁에 갇혀 출구를 찾지 못한 채, 되돌아갈 수도 없게 된 걸까?&lt;br&gt;원진의 유혹을 듣고 심연에 속아 넘어간 걸까?&lt;br&gt;아니면 그녀가 추구한 사도가 그녀로 하여금 너무 많은 것을 묻게 하고, 너무 많은 것을 바라게 한 끝에,&lt;br&gt;한꺼번에 그 대가를 치르게 된 걸까?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금 이 차가운 죽음의 물결 속에 있는 그녀는 또 어떤 심정일까?&lt;br&gt;여전히 당신이 익히 아는 그 호탕하고 자유로운 모습일까?&lt;br&gt;아니면 그녀가 배웅한 수많은 망령처럼, 혼란스럽고 고통스러워, 오래도록 배회하고 있을까?&lt;br&gt;그녀는 자신이 추구해 온 생사의 초월이, 백 년 후에도 여전히 헛된 말에 불과하다는 것과, 그녀가 구한 도 또한 끝없는 밤 아래 잠깐 스쳐 지나가는 미미한 빛 하나에 지나지 않는다는 사실을 알고 있을까?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6094,7 +6078,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -6213,7 +6197,7 @@
     </row>
     <row r="54" spans="1:4" ht="64" x14ac:dyDescent="0.45">
       <c r="C54" s="6" t="s">
-        <v>1613</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
@@ -6231,7 +6215,7 @@
         <v>10</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="D57" s="2">
         <v>1</v>
@@ -6639,7 +6623,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -6690,7 +6674,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>1596</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="48" x14ac:dyDescent="0.45">
@@ -6974,7 +6958,7 @@
     </row>
     <row r="63" spans="1:3" ht="64" x14ac:dyDescent="0.45">
       <c r="C63" s="4" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -7090,7 +7074,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="32" x14ac:dyDescent="0.45">
@@ -7108,7 +7092,7 @@
         <v>9</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
       <c r="D85" s="2">
         <v>1</v>
@@ -7119,7 +7103,7 @@
         <v>9</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>1607</v>
+        <v>1599</v>
       </c>
       <c r="D86" s="2">
         <v>1</v>
@@ -7155,7 +7139,7 @@
     </row>
     <row r="92" spans="1:4" ht="80" x14ac:dyDescent="0.45">
       <c r="C92" s="4" t="s">
-        <v>1611</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.45">
@@ -7203,7 +7187,7 @@
         <v>68</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>1608</v>
+        <v>1600</v>
       </c>
       <c r="D98" s="2">
         <v>1</v>
@@ -7271,7 +7255,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B108" s="3" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>246</v>
@@ -7724,7 +7708,7 @@
         <v>115</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>1597</v>
+        <v>1589</v>
       </c>
       <c r="D180" s="2">
         <v>1</v>
@@ -7838,7 +7822,7 @@
         <v>78</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
       <c r="D198" s="2">
         <v>1</v>
@@ -7849,7 +7833,7 @@
         <v>79</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="D199" s="2">
         <v>1</v>
@@ -7878,7 +7862,7 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A203" s="2" t="s">
-        <v>1602</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="48" x14ac:dyDescent="0.45">
@@ -7930,7 +7914,7 @@
     </row>
     <row r="211" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="C211" s="4" t="s">
-        <v>1600</v>
+        <v>1592</v>
       </c>
       <c r="D211" s="2">
         <v>1</v>
@@ -7965,7 +7949,7 @@
         <v>79</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.45">
@@ -8042,7 +8026,7 @@
         <v>803</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="48" x14ac:dyDescent="0.45">
@@ -8098,7 +8082,7 @@
         <v>141</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -8129,7 +8113,7 @@
         <v>141</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -8140,7 +8124,7 @@
         <v>141</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="D242" s="2">
         <v>1</v>
@@ -8230,7 +8214,7 @@
     </row>
     <row r="257" spans="2:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C257" s="4" t="s">
-        <v>1612</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="258" spans="2:3" ht="32" x14ac:dyDescent="0.45">
@@ -8388,7 +8372,7 @@
     </row>
     <row r="20" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C20" s="6" t="s">
-        <v>1618</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -8536,7 +8520,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>1614</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -8675,7 +8659,7 @@
     </row>
     <row r="66" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C66" s="6" t="s">
-        <v>1615</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.45">
@@ -9028,7 +9012,7 @@
     </row>
     <row r="121" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C121" s="7" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -10059,7 +10043,7 @@
         <v>559</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>1641</v>
+        <v>1633</v>
       </c>
       <c r="D282" s="2">
         <v>1</v>
@@ -10080,7 +10064,7 @@
         <v>559</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="D285" s="2">
         <v>1</v>
@@ -10101,7 +10085,7 @@
         <v>415</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>1620</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.45">
@@ -10463,7 +10447,7 @@
     </row>
     <row r="8" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C8" s="6" t="s">
-        <v>1621</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
@@ -10735,7 +10719,7 @@
     </row>
     <row r="54" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="C54" s="6" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.45">
@@ -10743,7 +10727,7 @@
         <v>721</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>1625</v>
+        <v>1617</v>
       </c>
       <c r="D55" s="2">
         <v>1</v>
@@ -10754,7 +10738,7 @@
         <v>721</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>1626</v>
+        <v>1618</v>
       </c>
       <c r="D56" s="2">
         <v>1</v>
@@ -11076,7 +11060,7 @@
     </row>
     <row r="109" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C109" s="6" t="s">
-        <v>1627</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="32" x14ac:dyDescent="0.45">
@@ -11255,7 +11239,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C137" s="6" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.45">
@@ -11430,7 +11414,7 @@
         <v>803</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>1628</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.45">
@@ -11547,7 +11531,7 @@
     </row>
     <row r="185" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="C185" s="6" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.45">
@@ -11692,7 +11676,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{002270F9-AB7B-4E5F-80E1-7221F0D19A97}">
-  <dimension ref="A1:F457"/>
+  <dimension ref="A1:F451"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
@@ -11747,12 +11731,12 @@
         <v>415</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1134</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C6" s="6" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -11790,7 +11774,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C13" s="6" t="s">
-        <v>1637</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
@@ -11819,7 +11803,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C17" s="6" t="s">
-        <v>1097</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.45">
@@ -11876,7 +11860,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>1226</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="32" x14ac:dyDescent="0.45">
@@ -11889,7 +11873,7 @@
         <v>415</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="48" x14ac:dyDescent="0.45">
@@ -11904,7 +11888,7 @@
     </row>
     <row r="31" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="C31" s="6" t="s">
-        <v>1098</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="48" x14ac:dyDescent="0.45">
@@ -11922,7 +11906,7 @@
         <v>415</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -11935,7 +11919,7 @@
         <v>415</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -11943,7 +11927,7 @@
         <v>415</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
@@ -11956,7 +11940,7 @@
     </row>
     <row r="39" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C39" s="6" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
@@ -11980,7 +11964,7 @@
         <v>16</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="64" x14ac:dyDescent="0.45">
@@ -11988,7 +11972,7 @@
         <v>415</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
@@ -11996,7 +11980,7 @@
         <v>415</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.45">
@@ -12004,7 +11988,7 @@
         <v>415</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12027,7 +12011,7 @@
         <v>415</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12040,12 +12024,12 @@
         <v>415</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C53" s="6" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12071,7 +12055,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.45">
@@ -12079,7 +12063,7 @@
         <v>16</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.45">
@@ -12087,7 +12071,7 @@
         <v>415</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>1143</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.45">
@@ -12100,7 +12084,7 @@
         <v>415</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.45">
@@ -12108,7 +12092,7 @@
         <v>16</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12121,12 +12105,12 @@
         <v>415</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C65" s="6" t="s">
-        <v>1639</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12134,7 +12118,7 @@
         <v>415</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>1146</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12142,7 +12126,7 @@
         <v>415</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12155,7 +12139,7 @@
         <v>415</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12163,7 +12147,7 @@
         <v>415</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>1149</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.45">
@@ -12171,7 +12155,7 @@
         <v>415</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.45">
@@ -12179,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.45">
@@ -12187,7 +12171,7 @@
         <v>415</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>1151</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.45">
@@ -12203,12 +12187,12 @@
         <v>415</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>1152</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C76" s="6" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="64" x14ac:dyDescent="0.45">
@@ -12216,7 +12200,7 @@
         <v>16</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>1232</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.45">
@@ -12224,7 +12208,7 @@
         <v>16</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12232,7 +12216,7 @@
         <v>16</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12245,7 +12229,7 @@
         <v>414</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>1153</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12258,7 +12242,7 @@
         <v>414</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>1154</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12266,7 +12250,7 @@
         <v>414</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>1155</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12279,7 +12263,7 @@
         <v>414</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>1156</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12287,7 +12271,7 @@
         <v>414</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>1157</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12300,7 +12284,7 @@
         <v>414</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>1158</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12308,7 +12292,7 @@
         <v>414</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>1159</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12316,7 +12300,7 @@
         <v>414</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>1160</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12326,12 +12310,12 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C93" s="6" t="s">
-        <v>1101</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C94" s="6" t="s">
-        <v>1102</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.45">
@@ -12352,7 +12336,7 @@
         <v>414</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>1161</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12360,7 +12344,7 @@
         <v>16</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12368,7 +12352,7 @@
         <v>16</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.45">
@@ -12376,7 +12360,7 @@
         <v>414</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>1162</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12389,12 +12373,12 @@
         <v>16</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C103" s="6" t="s">
-        <v>1103</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12402,7 +12386,7 @@
         <v>16</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.45">
@@ -12410,7 +12394,7 @@
         <v>16</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12418,7 +12402,7 @@
         <v>414</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>1163</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.45">
@@ -12439,7 +12423,7 @@
         <v>414</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12447,7 +12431,7 @@
         <v>16</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.45">
@@ -12455,7 +12439,7 @@
         <v>414</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>1165</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12463,7 +12447,7 @@
         <v>16</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.45">
@@ -12481,7 +12465,7 @@
         <v>414</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>1166</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12489,7 +12473,7 @@
         <v>414</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>1167</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.45">
@@ -12515,7 +12499,7 @@
         <v>414</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>1168</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12523,7 +12507,7 @@
         <v>414</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>1169</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12536,7 +12520,7 @@
         <v>414</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>1170</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12544,7 +12528,7 @@
         <v>414</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>1638</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12552,7 +12536,7 @@
         <v>414</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>1171</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.45">
@@ -12560,7 +12544,7 @@
         <v>414</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>1172</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.45">
@@ -12586,7 +12570,7 @@
         <v>16</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.45">
@@ -12594,7 +12578,7 @@
         <v>16</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.45">
@@ -12607,7 +12591,7 @@
         <v>415</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>1173</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12615,12 +12599,12 @@
         <v>415</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>1174</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C135" s="6" t="s">
-        <v>1104</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12633,7 +12617,7 @@
         <v>415</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>1175</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.45">
@@ -12646,7 +12630,7 @@
         <v>415</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>1176</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12654,7 +12638,7 @@
         <v>16</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.45">
@@ -12675,7 +12659,7 @@
         <v>415</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>1177</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -12705,7 +12689,7 @@
     </row>
     <row r="149" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C149" s="6" t="s">
-        <v>1105</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.45">
@@ -12817,7 +12801,7 @@
     </row>
     <row r="169" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C169" s="6" t="s">
-        <v>1106</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="170" spans="2:3" x14ac:dyDescent="0.45">
@@ -12843,7 +12827,7 @@
         <v>79</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="174" spans="2:3" x14ac:dyDescent="0.45">
@@ -12851,7 +12835,7 @@
         <v>79</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="175" spans="2:3" x14ac:dyDescent="0.45">
@@ -12864,7 +12848,7 @@
         <v>16</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.45">
@@ -12885,7 +12869,7 @@
         <v>16</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.45">
@@ -12911,7 +12895,7 @@
         <v>16</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -12924,7 +12908,7 @@
         <v>16</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.45">
@@ -13021,7 +13005,7 @@
         <v>79</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="64" x14ac:dyDescent="0.45">
@@ -13054,7 +13038,7 @@
         <v>79</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13102,12 +13086,12 @@
         <v>79</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C219" s="6" t="s">
-        <v>1107</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13140,7 +13124,7 @@
         <v>16</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="32" x14ac:dyDescent="0.45">
@@ -13153,7 +13137,7 @@
         <v>978</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>1108</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="228" spans="1:6" ht="32" x14ac:dyDescent="0.45">
@@ -13197,7 +13181,7 @@
     </row>
     <row r="234" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C234" s="6" t="s">
-        <v>1109</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.45">
@@ -13217,7 +13201,7 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C238" s="6" t="s">
-        <v>1110</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.45">
@@ -13238,7 +13222,7 @@
         <v>415</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>1178</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.45">
@@ -13246,7 +13230,7 @@
         <v>415</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>1179</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.45">
@@ -13274,7 +13258,7 @@
         <v>415</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.45">
@@ -13282,7 +13266,7 @@
         <v>415</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13295,7 +13279,7 @@
         <v>16</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.45">
@@ -13303,7 +13287,7 @@
         <v>5</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.45">
@@ -13311,7 +13295,7 @@
         <v>415</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.45">
@@ -13335,7 +13319,7 @@
         <v>16</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13343,7 +13327,7 @@
         <v>415</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>1182</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.45">
@@ -13356,7 +13340,7 @@
         <v>16</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13364,7 +13348,7 @@
         <v>415</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13372,7 +13356,7 @@
         <v>415</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>1184</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.45">
@@ -13380,7 +13364,7 @@
         <v>415</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>1185</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13406,7 +13390,7 @@
         <v>415</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>1186</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13414,7 +13398,7 @@
         <v>16</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13422,7 +13406,7 @@
         <v>415</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>1187</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13430,7 +13414,7 @@
         <v>415</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>1188</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13438,7 +13422,7 @@
         <v>415</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>1189</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13451,7 +13435,7 @@
         <v>16</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="64" x14ac:dyDescent="0.45">
@@ -13459,7 +13443,7 @@
         <v>415</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>1190</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13467,7 +13451,7 @@
         <v>415</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>1191</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="64" x14ac:dyDescent="0.45">
@@ -13480,7 +13464,7 @@
         <v>16</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13493,7 +13477,7 @@
         <v>415</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>1192</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.45">
@@ -13501,7 +13485,7 @@
         <v>16</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13514,7 +13498,7 @@
         <v>415</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13522,7 +13506,7 @@
         <v>415</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>1194</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13543,7 +13527,7 @@
         <v>415</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>1195</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13551,7 +13535,7 @@
         <v>415</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>1196</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.45">
@@ -13559,7 +13543,7 @@
         <v>5</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.45">
@@ -13572,7 +13556,7 @@
         <v>415</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>1197</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13580,7 +13564,7 @@
         <v>415</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>1629</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.45">
@@ -13590,12 +13574,12 @@
     </row>
     <row r="292" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C292" s="6" t="s">
-        <v>1096</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C293" s="6" t="s">
-        <v>1114</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.45">
@@ -13642,7 +13626,7 @@
         <v>415</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>1198</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="64" x14ac:dyDescent="0.45">
@@ -13650,7 +13634,7 @@
         <v>415</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>1199</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.45">
@@ -13658,7 +13642,7 @@
         <v>415</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>1200</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="64" x14ac:dyDescent="0.45">
@@ -13666,7 +13650,7 @@
         <v>415</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>1201</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13674,7 +13658,7 @@
         <v>415</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>1202</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13682,7 +13666,7 @@
         <v>415</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>1203</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13690,7 +13674,7 @@
         <v>415</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>1204</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13708,7 +13692,7 @@
         <v>415</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>1205</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13716,7 +13700,7 @@
         <v>415</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>1206</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.45">
@@ -13724,7 +13708,7 @@
         <v>415</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.45">
@@ -13755,7 +13739,7 @@
         <v>16</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13763,7 +13747,7 @@
         <v>16</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13771,7 +13755,7 @@
         <v>415</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>1208</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.45">
@@ -13787,7 +13771,7 @@
         <v>415</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>1209</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.45">
@@ -13803,7 +13787,7 @@
         <v>16</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>1259</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.45">
@@ -13811,7 +13795,7 @@
         <v>16</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>1260</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13824,7 +13808,7 @@
         <v>415</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>1210</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -13837,7 +13821,7 @@
         <v>415</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>1211</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.45">
@@ -13855,7 +13839,7 @@
         <v>415</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>1212</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.45">
@@ -13863,7 +13847,7 @@
         <v>415</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -13883,7 +13867,7 @@
     </row>
     <row r="335" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C335" s="6" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.45">
@@ -13891,770 +13875,740 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="337" spans="1:4" ht="48" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C337" s="6" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="338" spans="1:4" ht="48" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C338" s="6" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="48" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C339" s="6" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" ht="48" x14ac:dyDescent="0.45">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C340" s="6" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.45">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A341" s="2" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A342" s="2" t="s">
+        <v>803</v>
+      </c>
       <c r="C342" s="6" t="s">
         <v>1022</v>
       </c>
       <c r="D342" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="F342" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" ht="64" x14ac:dyDescent="0.45">
+      <c r="A343" s="2" t="s">
+        <v>803</v>
+      </c>
       <c r="C343" s="6" t="s">
-        <v>1023</v>
+        <v>1635</v>
       </c>
       <c r="D343" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="F343" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" ht="96" x14ac:dyDescent="0.45">
+      <c r="A344" s="2" t="s">
+        <v>803</v>
+      </c>
       <c r="C344" s="6" t="s">
-        <v>1024</v>
+        <v>1636</v>
       </c>
       <c r="D344" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="345" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="F344" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C345" s="6" t="s">
-        <v>1025</v>
+        <v>1110</v>
       </c>
       <c r="D345" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C346" s="6" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="D346" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C347" s="6" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D347" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A347" s="2" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C348" s="6" t="s">
-        <v>1028</v>
+        <v>1111</v>
       </c>
       <c r="D348" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C349" s="6" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C350" s="6" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A351" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B352" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C352" s="6" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A353" s="2" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C354" s="6" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B355" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C356" s="6" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C357" s="6" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A358" s="2" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C359" s="6" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B360" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B361" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+      <c r="C362" s="6" t="s">
         <v>1029</v>
       </c>
-      <c r="D349" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4" ht="48" x14ac:dyDescent="0.45">
-      <c r="C350" s="6" t="s">
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C363" s="6" t="s">
         <v>1030</v>
       </c>
-      <c r="D350" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="C351" s="6" t="s">
-        <v>1118</v>
-      </c>
-      <c r="D351" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C352" s="6" t="s">
+    </row>
+    <row r="364" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C364" s="6" t="s">
         <v>1031</v>
       </c>
-      <c r="D352" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A353" s="2" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C354" s="6" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D354" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" ht="48" x14ac:dyDescent="0.45">
-      <c r="C355" s="6" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C356" s="6" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A357" s="2" t="s">
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C365" s="6" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A366" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C357" s="6" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B358" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C358" s="6" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A359" s="2" t="s">
+      <c r="C366" s="6" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="C360" s="6" t="s">
+    <row r="367" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B367" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C367" s="6" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B368" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C368" s="6" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C369" s="6" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B361" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C361" s="6" t="s">
-        <v>1213</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C362" s="6" t="s">
+    <row r="370" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="B370" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+      <c r="C371" s="6" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C363" s="6" t="s">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B372" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C372" s="6" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C373" s="6" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A364" s="2" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="C365" s="6" t="s">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C374" s="6" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A375" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A376" s="2" t="s">
         <v>1036</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="B366" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C366" s="6" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="B367" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C367" s="6" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4" ht="48" x14ac:dyDescent="0.45">
-      <c r="C368" s="6" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C369" s="6" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C370" s="6" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C371" s="6" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A372" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C372" s="6" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B373" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C373" s="6" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B374" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C374" s="6" t="s">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C375" s="6" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="B376" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C376" s="6" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C377" s="6" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C378" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B379" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C379" s="6" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A380" s="2" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+      <c r="C381" s="6" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B382" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C383" s="6" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A384" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C384" s="6" t="s">
         <v>1042</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B378" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C378" s="6" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C379" s="6" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C380" s="6" t="s">
-        <v>1123</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A381" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A382" s="2" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" ht="48" x14ac:dyDescent="0.45">
-      <c r="C383" s="6" t="s">
-        <v>1045</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C384" s="6" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B385" s="3" t="s">
-        <v>415</v>
+        <v>16</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>1220</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A386" s="2" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="C387" s="6" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" ht="48" x14ac:dyDescent="0.45">
+      <c r="C388" s="6" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="C389" s="6" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" ht="48" x14ac:dyDescent="0.45">
+      <c r="C390" s="6" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" ht="64" x14ac:dyDescent="0.45">
+      <c r="C391" s="6" t="s">
         <v>1047</v>
       </c>
     </row>
-    <row r="387" spans="1:4" ht="48" x14ac:dyDescent="0.45">
-      <c r="C387" s="6" t="s">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B392" s="3" t="s">
         <v>1048</v>
       </c>
-    </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B388" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C388" s="6" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C389" s="6" t="s">
+      <c r="C392" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D392" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A393" s="2" t="s">
         <v>1049</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A390" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C390" s="6" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B391" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C391" s="6" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A392" s="2" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="393" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="C393" s="6" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="C394" s="6" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B395" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C395" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D395" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A396" s="2" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="C397" s="6" t="s">
         <v>1052</v>
       </c>
     </row>
-    <row r="395" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="C395" s="6" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="396" spans="1:4" ht="48" x14ac:dyDescent="0.45">
-      <c r="C396" s="6" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="397" spans="1:4" ht="64" x14ac:dyDescent="0.45">
-      <c r="C397" s="6" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B398" s="3" t="s">
-        <v>1056</v>
-      </c>
+    <row r="398" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="C398" s="6" t="s">
-        <v>1125</v>
-      </c>
-      <c r="D398" s="2">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C399" s="6" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="B400" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C400" s="6" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D400" s="2">
         <v>1</v>
-      </c>
-    </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A399" s="2" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="400" spans="1:4" ht="48" x14ac:dyDescent="0.45">
-      <c r="C400" s="6" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B401" s="3" t="s">
-        <v>1056</v>
+        <v>1048</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>1126</v>
+        <v>1622</v>
       </c>
       <c r="D401" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A402" s="2" t="s">
-        <v>1059</v>
+      <c r="B402" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C402" s="6" t="s">
+        <v>1255</v>
       </c>
     </row>
     <row r="403" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C403" s="6" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C404" s="6" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C405" s="6" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A406" s="2" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A407" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C407" s="6" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F407" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A408" s="2" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B409" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C409" s="6" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B410" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C410" s="6" t="s">
         <v>1060</v>
       </c>
     </row>
-    <row r="404" spans="1:6" ht="48" x14ac:dyDescent="0.45">
-      <c r="C404" s="6" t="s">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A411" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+      <c r="C412" s="6" t="s">
         <v>1061</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C405" s="6" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="406" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="B406" s="3" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C406" s="6" t="s">
-        <v>1128</v>
-      </c>
-      <c r="D406" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B407" s="3" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C407" s="6" t="s">
-        <v>1630</v>
-      </c>
-      <c r="D407" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B408" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C408" s="6" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="409" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C409" s="6" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="C410" s="6" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="411" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C411" s="6" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A412" s="2" t="s">
-        <v>1065</v>
-      </c>
-    </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A413" s="2" t="s">
-        <v>803</v>
+      <c r="B413" s="3" t="s">
+        <v>415</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F413" s="2">
-        <v>14</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A414" s="2" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B415" s="3" t="s">
-        <v>415</v>
-      </c>
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C415" s="6" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B416" s="3" t="s">
-        <v>415</v>
-      </c>
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C416" s="6" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A417" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B418" s="3" t="s">
+        <v>415</v>
+      </c>
       <c r="C418" s="6" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B419" s="3" t="s">
-        <v>415</v>
-      </c>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C419" s="6" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A420" s="2" t="s">
         <v>1065</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="C420" s="6" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C421" s="6" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C422" s="6" t="s">
-        <v>1071</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A423" s="2" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B424" s="3" t="s">
-        <v>415</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C423" s="6" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" ht="64" x14ac:dyDescent="0.45">
       <c r="C424" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C425" s="6" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" ht="32" x14ac:dyDescent="0.45">
-      <c r="C426" s="6" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" ht="48" x14ac:dyDescent="0.45">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A426" s="2" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C427" s="6" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C428" s="6" t="s">
-        <v>1131</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A429" s="2" t="s">
-        <v>5</v>
+      <c r="B429" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" ht="64" x14ac:dyDescent="0.45">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B430" s="3" t="s">
+        <v>415</v>
+      </c>
       <c r="C430" s="6" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.45">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C431" s="6" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A432" s="2" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.45">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C433" s="6" t="s">
-        <v>1132</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B434" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="C434" s="6" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B435" s="3" t="s">
-        <v>10</v>
-      </c>
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6" ht="64" x14ac:dyDescent="0.45">
       <c r="C435" s="6" t="s">
-        <v>1273</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B436" s="3" t="s">
-        <v>415</v>
+        <v>1075</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="437" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C437" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D436" s="2">
+        <v>1</v>
+      </c>
+      <c r="F436" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A437" s="2" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+      <c r="C438" s="6" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B439" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C439" s="6" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C440" s="6" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C441" s="6" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="C442" s="6" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B443" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C443" s="6" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B444" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C444" s="6" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+      <c r="C445" s="6" t="s">
         <v>1080</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A438" s="2" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="439" spans="1:6" ht="48" x14ac:dyDescent="0.45">
-      <c r="C439" s="6" t="s">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B440" s="3" t="s">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="B446" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C440" s="6" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="441" spans="1:6" ht="64" x14ac:dyDescent="0.45">
-      <c r="C441" s="6" t="s">
+      <c r="C446" s="6" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A447" s="2" t="s">
         <v>1082</v>
-      </c>
-    </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B442" s="3" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C442" s="6" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D442" s="2">
-        <v>1</v>
-      </c>
-      <c r="F442" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A443" s="2" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="444" spans="1:6" ht="48" x14ac:dyDescent="0.45">
-      <c r="C444" s="6" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B445" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C445" s="6" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="446" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C446" s="6" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="447" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C447" s="6" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="448" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C448" s="6" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B449" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C449" s="6" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B450" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="A449" s="2" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C450" s="6" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="451" spans="1:6" ht="48" x14ac:dyDescent="0.45">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6" ht="32" x14ac:dyDescent="0.45">
+      <c r="A451" s="2" t="s">
+        <v>803</v>
+      </c>
       <c r="C451" s="6" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="B452" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C452" s="6" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A453" s="2" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="454" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C454" s="6" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A455" s="2" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="456" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="C456" s="6" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="457" spans="1:6" ht="32" x14ac:dyDescent="0.45">
-      <c r="A457" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="C457" s="6" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F457" s="2">
+        <v>1086</v>
+      </c>
+      <c r="F451" s="2">
         <v>24</v>
       </c>
     </row>
@@ -14706,7 +14660,7 @@
         <v>803</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="F3" s="2">
         <v>24</v>
@@ -14719,17 +14673,17 @@
     </row>
     <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C5" s="6" t="s">
-        <v>1631</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C6" s="6" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>1275</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -14737,12 +14691,12 @@
         <v>415</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C9" s="6" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -14750,7 +14704,7 @@
         <v>415</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1421</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -14758,7 +14712,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.45">
@@ -14766,22 +14720,22 @@
         <v>16</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C13" s="6" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C14" s="6" t="s">
-        <v>1278</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C15" s="6" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.45">
@@ -14789,7 +14743,7 @@
         <v>415</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
@@ -14797,7 +14751,7 @@
         <v>415</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1425</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
@@ -14805,32 +14759,32 @@
         <v>415</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1426</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C20" s="6" t="s">
-        <v>1281</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>1283</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C22" s="6" t="s">
-        <v>1549</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C23" s="6" t="s">
-        <v>1282</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -14838,7 +14792,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1404</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -14846,12 +14800,12 @@
         <v>16</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C26" s="6" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -14859,7 +14813,7 @@
         <v>415</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -14867,7 +14821,7 @@
         <v>415</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1428</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -14875,22 +14829,22 @@
         <v>415</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="64" x14ac:dyDescent="0.45">
       <c r="C30" s="6" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C31" s="6" t="s">
-        <v>1430</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C32" s="6" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
@@ -14898,12 +14852,12 @@
         <v>415</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1406</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C34" s="6" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -14911,7 +14865,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -14919,22 +14873,22 @@
         <v>415</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C37" s="6" t="s">
-        <v>1288</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="64" x14ac:dyDescent="0.45">
       <c r="C38" s="6" t="s">
-        <v>1550</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C39" s="6" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
@@ -14942,22 +14896,22 @@
         <v>5</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C42" s="6" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C43" s="6" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
@@ -14965,7 +14919,7 @@
         <v>415</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>1434</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
@@ -14973,7 +14927,7 @@
         <v>16</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>1435</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="64" x14ac:dyDescent="0.45">
@@ -14981,7 +14935,7 @@
         <v>16</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -14989,7 +14943,7 @@
         <v>16</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>1497</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
@@ -15002,12 +14956,12 @@
     </row>
     <row r="49" spans="2:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C49" s="6" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="50" spans="2:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C50" s="6" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="51" spans="2:3" ht="64" x14ac:dyDescent="0.45">
@@ -15015,12 +14969,12 @@
         <v>16</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C52" s="6" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="53" spans="2:3" ht="48" x14ac:dyDescent="0.45">
@@ -15028,7 +14982,7 @@
         <v>16</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="32" x14ac:dyDescent="0.45">
@@ -15036,17 +14990,17 @@
         <v>16</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="55" spans="2:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C55" s="6" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C56" s="6" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.45">
@@ -15054,7 +15008,7 @@
         <v>16</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>1437</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="58" spans="2:3" ht="48" x14ac:dyDescent="0.45">
@@ -15062,17 +15016,17 @@
         <v>16</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>1551</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="59" spans="2:3" ht="64" x14ac:dyDescent="0.45">
       <c r="C59" s="6" t="s">
-        <v>1438</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C60" s="6" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="61" spans="2:3" ht="48" x14ac:dyDescent="0.45">
@@ -15080,7 +15034,7 @@
         <v>415</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>1439</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="48" x14ac:dyDescent="0.45">
@@ -15088,12 +15042,12 @@
         <v>415</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>1440</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="63" spans="2:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C63" s="6" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="64" spans="2:3" ht="32" x14ac:dyDescent="0.45">
@@ -15101,7 +15055,7 @@
         <v>415</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -15109,17 +15063,17 @@
         <v>415</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>1552</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C66" s="6" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C67" s="6" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -15127,7 +15081,7 @@
         <v>16</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="64" x14ac:dyDescent="0.45">
@@ -15135,12 +15089,12 @@
         <v>16</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C70" s="6" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.45">
@@ -15148,7 +15102,7 @@
         <v>415</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.45">
@@ -15156,12 +15110,12 @@
         <v>415</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C73" s="6" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.45">
@@ -15171,37 +15125,37 @@
     </row>
     <row r="75" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C75" s="6" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C76" s="6" t="s">
-        <v>1303</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="64" x14ac:dyDescent="0.45">
       <c r="C77" s="6" t="s">
-        <v>1553</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C78" s="6" t="s">
-        <v>1554</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C79" s="6" t="s">
-        <v>1304</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
-        <v>1307</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C81" s="6" t="s">
-        <v>1305</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.45">
@@ -15209,7 +15163,7 @@
         <v>16</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -15217,12 +15171,12 @@
         <v>415</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C84" s="6" t="s">
-        <v>1306</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.45">
@@ -15230,12 +15184,12 @@
         <v>415</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>1413</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C86" s="6" t="s">
-        <v>1308</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.45">
@@ -15250,27 +15204,27 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C89" s="6" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
-        <v>1309</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C91" s="6" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C92" s="6" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C93" s="6" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -15278,7 +15232,7 @@
         <v>145</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -15286,12 +15240,12 @@
         <v>145</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C96" s="6" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -15299,22 +15253,22 @@
         <v>16</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C98" s="6" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C100" s="6" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.45">
@@ -15327,12 +15281,12 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C102" s="6" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C103" s="6" t="s">
-        <v>1317</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.45">
@@ -15340,22 +15294,22 @@
         <v>16</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C105" s="6" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C107" s="6" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.45">
@@ -15363,12 +15317,12 @@
         <v>16</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>1414</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C109" s="6" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -15376,43 +15330,43 @@
         <v>145</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>1634</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B111" s="3" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C112" s="6" t="s">
-        <v>1322</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C113" s="6" t="s">
-        <v>1323</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C114" s="6" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C115" s="6" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.45">
       <c r="B116" s="3" t="s">
-        <v>1083</v>
+        <v>1075</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="D116" s="2">
         <v>1</v>
@@ -15423,32 +15377,32 @@
     </row>
     <row r="117" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C117" s="6" t="s">
-        <v>1454</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A118" s="2" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C119" s="6" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C120" s="6" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C121" s="6" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C122" s="6" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.45">
@@ -15461,7 +15415,7 @@
     </row>
     <row r="124" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C124" s="6" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.45">
@@ -15469,7 +15423,7 @@
         <v>5</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
       <c r="E125" s="2">
         <v>1</v>
@@ -15477,27 +15431,27 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A126" s="2" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C127" s="6" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C128" s="6" t="s">
-        <v>1457</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A129" s="2" t="s">
-        <v>1092</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C130" s="6" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.45">
@@ -15507,17 +15461,17 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C132" s="6" t="s">
-        <v>1458</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A133" s="2" t="s">
-        <v>1309</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C134" s="6" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.45">
@@ -15527,12 +15481,12 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C136" s="6" t="s">
-        <v>1459</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C137" s="6" t="s">
-        <v>1335</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.45">
@@ -15542,27 +15496,27 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C139" s="6" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A140" s="2" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C141" s="6" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C142" s="6" t="s">
-        <v>1460</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C143" s="6" t="s">
-        <v>1339</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.45">
@@ -15575,7 +15529,7 @@
         <v>16</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.45">
@@ -15583,7 +15537,7 @@
         <v>16</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>1340</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -15591,17 +15545,17 @@
         <v>16</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C148" s="6" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C149" s="6" t="s">
-        <v>1342</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -15609,7 +15563,7 @@
         <v>16</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.45">
@@ -15617,7 +15571,7 @@
         <v>16</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>1498</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -15625,7 +15579,7 @@
         <v>16</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>1555</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -15633,7 +15587,7 @@
         <v>16</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>1556</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.45">
@@ -15641,12 +15595,12 @@
         <v>5</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>1343</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C155" s="6" t="s">
-        <v>1344</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.45">
@@ -15654,7 +15608,7 @@
         <v>16</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>1462</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.45">
@@ -15662,7 +15616,7 @@
         <v>16</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>1463</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -15670,7 +15624,7 @@
         <v>16</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>1464</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.45">
@@ -15678,12 +15632,12 @@
         <v>16</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C160" s="6" t="s">
-        <v>1345</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.45">
@@ -15691,7 +15645,7 @@
         <v>16</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>1465</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.45">
@@ -15699,17 +15653,17 @@
         <v>16</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>1418</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C163" s="6" t="s">
-        <v>1466</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C164" s="6" t="s">
-        <v>1346</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -15717,7 +15671,7 @@
         <v>16</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.45">
@@ -15725,7 +15679,7 @@
         <v>16</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>1467</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="48" x14ac:dyDescent="0.45">
@@ -15733,17 +15687,17 @@
         <v>16</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>1557</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C168" s="6" t="s">
-        <v>1347</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C169" s="6" t="s">
-        <v>1348</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.45">
@@ -15751,22 +15705,22 @@
         <v>16</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>1468</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C171" s="6" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C172" s="6" t="s">
-        <v>1469</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C173" s="6" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.45">
@@ -15776,7 +15730,7 @@
     </row>
     <row r="175" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C175" s="6" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.45">
@@ -15794,37 +15748,37 @@
     </row>
     <row r="178" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C178" s="6" t="s">
-        <v>1389</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C179" s="6" t="s">
-        <v>1352</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C180" s="6" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C181" s="6" t="s">
-        <v>1470</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C182" s="6" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C183" s="6" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C184" s="6" t="s">
-        <v>1471</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.45">
@@ -15832,22 +15786,22 @@
         <v>5</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>1356</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C186" s="6" t="s">
-        <v>1357</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C187" s="6" t="s">
-        <v>1558</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="64" x14ac:dyDescent="0.45">
       <c r="C188" s="6" t="s">
-        <v>1559</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.45">
@@ -15855,27 +15809,27 @@
         <v>5</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>1358</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C190" s="6" t="s">
-        <v>1359</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C191" s="6" t="s">
-        <v>1472</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C192" s="6" t="s">
-        <v>1473</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="48" x14ac:dyDescent="0.45">
       <c r="C193" s="6" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="32" x14ac:dyDescent="0.45">
@@ -15888,7 +15842,7 @@
     </row>
     <row r="195" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="C195" s="6" t="s">
-        <v>1361</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.45">
@@ -15896,7 +15850,7 @@
         <v>5</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>1362</v>
+        <v>1354</v>
       </c>
       <c r="E196" s="2">
         <v>1</v>
@@ -15904,22 +15858,22 @@
     </row>
     <row r="197" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="C197" s="6" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="64" x14ac:dyDescent="0.45">
       <c r="C198" s="6" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="C199" s="6" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.45">
       <c r="C200" s="6" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.45">
@@ -15927,7 +15881,7 @@
         <v>5</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
       <c r="E201" s="2">
         <v>1</v>
@@ -15935,22 +15889,22 @@
     </row>
     <row r="202" spans="1:5" ht="64" x14ac:dyDescent="0.45">
       <c r="C202" s="6" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="203" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="C203" s="6" t="s">
-        <v>1370</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.45">
       <c r="C204" s="6" t="s">
-        <v>1474</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="205" spans="1:5" ht="64" x14ac:dyDescent="0.45">
       <c r="C205" s="6" t="s">
-        <v>1369</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.45">
@@ -15958,7 +15912,7 @@
         <v>5</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
       <c r="E206" s="2">
         <v>1</v>
@@ -15966,22 +15920,22 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.45">
       <c r="C207" s="6" t="s">
-        <v>1475</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="208" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="C208" s="6" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C209" s="6" t="s">
-        <v>1372</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A210" s="2" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.45">
@@ -15989,32 +15943,32 @@
         <v>79</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="64" x14ac:dyDescent="0.45">
       <c r="C212" s="6" t="s">
-        <v>1373</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C213" s="6" t="s">
-        <v>1477</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C214" s="6" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C215" s="6" t="s">
-        <v>1560</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C216" s="6" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -16022,7 +15976,7 @@
         <v>79</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.45">
@@ -16030,7 +15984,7 @@
         <v>79</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.45">
@@ -16038,27 +15992,27 @@
         <v>79</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>1479</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C220" s="6" t="s">
-        <v>1480</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A221" s="2" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="64" x14ac:dyDescent="0.45">
       <c r="C222" s="6" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C223" s="6" t="s">
-        <v>1481</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.45">
@@ -16066,12 +16020,12 @@
         <v>5</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C225" s="6" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -16079,7 +16033,7 @@
         <v>415</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>1379</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.45">
@@ -16087,7 +16041,7 @@
         <v>415</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>1378</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.45">
@@ -16095,7 +16049,7 @@
         <v>415</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>1561</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.45">
@@ -16103,22 +16057,22 @@
         <v>5</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A230" s="2" t="s">
-        <v>1392</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C231" s="6" t="s">
-        <v>1380</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C232" s="6" t="s">
-        <v>1381</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.45">
@@ -16126,22 +16080,22 @@
         <v>5</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>1382</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C234" s="6" t="s">
-        <v>1383</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C235" s="6" t="s">
-        <v>1483</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C236" s="6" t="s">
-        <v>1484</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.45">
@@ -16149,7 +16103,7 @@
         <v>5</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.45">
@@ -16157,40 +16111,40 @@
         <v>5</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>1485</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A239" s="2" t="s">
-        <v>1393</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C240" s="6" t="s">
-        <v>1486</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A241" s="2" t="s">
-        <v>1394</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="C242" s="6" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A243" s="2" t="s">
-        <v>1395</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="B244" s="3" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>1499</v>
+        <v>1491</v>
       </c>
       <c r="D244" s="2">
         <v>1</v>
@@ -16198,10 +16152,10 @@
     </row>
     <row r="245" spans="1:4" ht="64" x14ac:dyDescent="0.45">
       <c r="B245" s="3" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="D245" s="2">
         <v>1</v>
@@ -16209,15 +16163,15 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A246" s="2" t="s">
-        <v>1396</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="B247" s="3" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>1500</v>
+        <v>1492</v>
       </c>
       <c r="D247" s="2">
         <v>1</v>
@@ -16225,15 +16179,15 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A248" s="2" t="s">
-        <v>1395</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="B249" s="3" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="D249" s="2">
         <v>1</v>
@@ -16241,10 +16195,10 @@
     </row>
     <row r="250" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="B250" s="3" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="D250" s="2">
         <v>1</v>
@@ -16252,15 +16206,15 @@
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A251" s="2" t="s">
-        <v>1397</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="64" x14ac:dyDescent="0.45">
       <c r="B252" s="3" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
       <c r="D252" s="2">
         <v>1</v>
@@ -16268,10 +16222,10 @@
     </row>
     <row r="253" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="B253" s="3" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>1503</v>
+        <v>1495</v>
       </c>
       <c r="D253" s="2">
         <v>1</v>
@@ -16279,25 +16233,25 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A254" s="2" t="s">
-        <v>1398</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="C255" s="6" t="s">
-        <v>1488</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A256" s="2" t="s">
-        <v>1399</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="B257" s="3" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="D257" s="2">
         <v>1</v>
@@ -16305,10 +16259,10 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B258" s="3" t="s">
-        <v>1384</v>
+        <v>1376</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>1490</v>
+        <v>1482</v>
       </c>
       <c r="D258" s="2">
         <v>1</v>
@@ -16316,12 +16270,12 @@
     </row>
     <row r="259" spans="1:4" ht="48" x14ac:dyDescent="0.45">
       <c r="C259" s="6" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A260" s="2" t="s">
-        <v>1400</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="48" x14ac:dyDescent="0.45">
@@ -16329,7 +16283,7 @@
         <v>415</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>1385</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="32" x14ac:dyDescent="0.45">
@@ -16337,17 +16291,17 @@
         <v>415</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A263" s="2" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C264" s="6" t="s">
-        <v>1386</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="32" x14ac:dyDescent="0.45">
@@ -16355,12 +16309,12 @@
         <v>16</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>1562</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="64" x14ac:dyDescent="0.45">
       <c r="C266" s="6" t="s">
-        <v>1387</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.45">
@@ -16368,12 +16322,12 @@
         <v>16</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>1493</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="32" x14ac:dyDescent="0.45">
       <c r="C268" s="6" t="s">
-        <v>1494</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.45">
@@ -16381,7 +16335,7 @@
         <v>16</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.45">
@@ -16394,7 +16348,7 @@
         <v>415</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>1413</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.45">
@@ -16402,205 +16356,205 @@
         <v>16</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>1496</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A273" s="2" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C274" s="6" t="s">
-        <v>1388</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A275" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>1505</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A276" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1506</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A277" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A278" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A279" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A280" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>1508</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C281" s="6" t="s">
-        <v>1511</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A282" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>1516</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A283" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C283" s="6" t="s">
         <v>1504</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>1510</v>
-      </c>
-      <c r="C283" s="6" t="s">
-        <v>1512</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A284" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A285" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>1514</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A286" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A287" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>1565</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="A288" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>1513</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="290" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="A290" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>1517</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A291" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B291" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C291" s="6" t="s">
         <v>1510</v>
-      </c>
-      <c r="C291" s="6" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A292" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A293" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>1566</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A294" s="2" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.45">
@@ -16610,22 +16564,22 @@
     </row>
     <row r="296" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C296" s="6" t="s">
-        <v>1520</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A297" s="2" t="s">
-        <v>1521</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="298" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C298" s="6" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="299" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C299" s="6" t="s">
-        <v>1567</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.45">
@@ -16633,7 +16587,7 @@
         <v>16</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>1580</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="301" spans="1:6" ht="32" x14ac:dyDescent="0.45">
@@ -16641,7 +16595,7 @@
         <v>16</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>1581</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="302" spans="1:6" ht="48" x14ac:dyDescent="0.45">
@@ -16649,7 +16603,7 @@
         <v>16</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>1582</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="303" spans="1:6" ht="32" x14ac:dyDescent="0.45">
@@ -16657,7 +16611,7 @@
         <v>803</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="F303" s="2">
         <v>24</v>
@@ -16668,27 +16622,27 @@
         <v>16</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="305" spans="1:6" ht="64" x14ac:dyDescent="0.45">
       <c r="C305" s="6" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="306" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C306" s="6" t="s">
-        <v>1523</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A307" s="2" t="s">
-        <v>1524</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="308" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C308" s="6" t="s">
-        <v>1525</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.45">
@@ -16696,27 +16650,27 @@
         <v>16</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="310" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C310" s="6" t="s">
-        <v>1526</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="311" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C311" s="6" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="312" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C312" s="6" t="s">
-        <v>1528</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C313" s="6" t="s">
-        <v>1527</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.45">
@@ -16724,7 +16678,7 @@
         <v>5</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>1529</v>
+        <v>1521</v>
       </c>
       <c r="D314" s="2">
         <v>1</v>
@@ -16738,42 +16692,42 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A315" s="2" t="s">
-        <v>1530</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="316" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C316" s="6" t="s">
-        <v>1563</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A317" s="2" t="s">
-        <v>1524</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="318" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C318" s="6" t="s">
-        <v>1590</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="319" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C319" s="6" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="320" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C320" s="6" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="321" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C321" s="6" t="s">
-        <v>1531</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C322" s="6" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.45">
@@ -16781,7 +16735,7 @@
         <v>16</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.45">
@@ -16789,27 +16743,27 @@
         <v>16</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C325" s="6" t="s">
-        <v>1533</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="326" spans="1:6" ht="48" x14ac:dyDescent="0.45">
       <c r="C326" s="6" t="s">
-        <v>1534</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="327" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C327" s="6" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C328" s="6" t="s">
-        <v>1535</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.45">
@@ -16822,7 +16776,7 @@
         <v>803</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="F330" s="2">
         <v>16</v>
@@ -16830,27 +16784,27 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A332" s="2" t="s">
-        <v>1537</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.45">
       <c r="C333" s="6" t="s">
-        <v>1564</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="334" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C334" s="6" t="s">
-        <v>1538</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="335" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C335" s="6" t="s">
-        <v>1571</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="336" spans="1:6" ht="32" x14ac:dyDescent="0.45">
       <c r="C336" s="6" t="s">
-        <v>1539</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.45">
@@ -16858,7 +16812,7 @@
         <v>415</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>1576</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -16866,27 +16820,27 @@
         <v>415</v>
       </c>
       <c r="C338" s="7" t="s">
-        <v>1593</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A339" s="2" t="s">
-        <v>1540</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="48" x14ac:dyDescent="0.45">
       <c r="C340" s="6" t="s">
-        <v>1541</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C341" s="6" t="s">
-        <v>1542</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C342" s="6" t="s">
-        <v>1572</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.45">
@@ -16897,7 +16851,7 @@
         <v>415</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -16905,7 +16859,7 @@
         <v>16</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.45">
@@ -16913,12 +16867,12 @@
         <v>16</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C346" s="6" t="s">
-        <v>1543</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -16926,7 +16880,7 @@
         <v>415</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>1577</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.45">
@@ -16934,27 +16888,27 @@
         <v>415</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>1578</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C349" s="6" t="s">
-        <v>1544</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.45">
       <c r="C350" s="6" t="s">
-        <v>1545</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="32" x14ac:dyDescent="0.45">
       <c r="C351" s="6" t="s">
-        <v>1546</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A352" s="2" t="s">
-        <v>1547</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -16962,7 +16916,7 @@
         <v>415</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>1635</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -16970,7 +16924,7 @@
         <v>415</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>1579</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.45">
@@ -16980,7 +16934,7 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A356" s="2" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="32" x14ac:dyDescent="0.45">
@@ -16988,7 +16942,7 @@
         <v>145</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>1574</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.45">
@@ -16996,7 +16950,7 @@
         <v>145</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>1575</v>
+        <v>1567</v>
       </c>
     </row>
   </sheetData>
